--- a/auto_eval测试用例清单.xlsx
+++ b/auto_eval测试用例清单.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9060" activeTab="1"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Information文档信息" sheetId="1" r:id="rId1"/>
@@ -125,7 +125,7 @@
     <t>完成 auto_eval.py 测试用例清单</t>
   </si>
   <si>
-    <t>汪嘉楠）</t>
+    <t xml:space="preserve">汪嘉楠 </t>
   </si>
   <si>
     <t>yyyy.mm.dd</t>
@@ -1978,8 +1978,8 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="3798570" y="6998970"/>
-        <a:ext cx="3566160" cy="2474595"/>
+        <a:off x="3883025" y="7129780"/>
+        <a:ext cx="3647440" cy="2486025"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -2251,12 +2251,12 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B1:L43"/>
-  <sheetFormatPr defaultColWidth="11.6363636363636" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="11.637037037037" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="1.63636363636364" style="9" customWidth="1"/>
-    <col min="2" max="13" width="10.6363636363636" style="9" customWidth="1"/>
-    <col min="14" max="15" width="7.63636363636364" style="9" customWidth="1"/>
-    <col min="16" max="16384" width="11.6363636363636" style="9" customWidth="1"/>
+    <col min="1" max="1" width="1.63703703703704" style="9" customWidth="1"/>
+    <col min="2" max="13" width="10.637037037037" style="9" customWidth="1"/>
+    <col min="14" max="15" width="7.63703703703704" style="9" customWidth="1"/>
+    <col min="16" max="16384" width="11.637037037037" style="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="9.9" customHeight="1"/>
@@ -2531,7 +2531,7 @@
       </c>
       <c r="L19" s="19"/>
     </row>
-    <row r="20" ht="16.2" customHeight="1" spans="2:12">
+    <row r="20" ht="25" customHeight="1" spans="2:12">
       <c r="B20" s="28" t="s">
         <v>14</v>
       </c>
@@ -2924,23 +2924,23 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:EJ12389"/>
-  <sheetFormatPr defaultColWidth="11.6363636363636" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="11.637037037037" defaultRowHeight="15.75"/>
   <cols>
-    <col min="1" max="1" width="15.3636363636364" style="8" customWidth="1"/>
-    <col min="2" max="2" width="16.5454545454545" style="8" customWidth="1"/>
-    <col min="3" max="3" width="26.8181818181818" style="8" customWidth="1"/>
+    <col min="1" max="1" width="15.362962962963" style="8" customWidth="1"/>
+    <col min="2" max="2" width="16.5481481481481" style="8" customWidth="1"/>
+    <col min="3" max="3" width="26.8148148148148" style="8" customWidth="1"/>
     <col min="4" max="4" width="21" style="8" customWidth="1"/>
-    <col min="5" max="5" width="13.9090909090909" style="8" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="8.90909090909091" style="8" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="21.1818181818182" style="8" customWidth="1"/>
-    <col min="8" max="8" width="12.8181818181818" style="8" customWidth="1"/>
-    <col min="9" max="9" width="14.4545454545455" style="8" customWidth="1"/>
-    <col min="10" max="10" width="16.4545454545455" style="8" customWidth="1"/>
-    <col min="11" max="11" width="11.8181818181818" style="8" customWidth="1"/>
+    <col min="5" max="5" width="13.9111111111111" style="8" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="8.91111111111111" style="8" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="21.1851851851852" style="8" customWidth="1"/>
+    <col min="8" max="8" width="12.8148148148148" style="8" customWidth="1"/>
+    <col min="9" max="9" width="14.4518518518519" style="8" customWidth="1"/>
+    <col min="10" max="10" width="16.4518518518519" style="8" customWidth="1"/>
+    <col min="11" max="11" width="11.8148148148148" style="8" customWidth="1"/>
     <col min="12" max="12" width="11" style="8" customWidth="1"/>
-    <col min="13" max="13" width="20.9090909090909" style="8" customWidth="1"/>
-    <col min="14" max="14" width="3.45454545454545" style="9" hidden="1" customWidth="1"/>
-    <col min="15" max="16384" width="11.6363636363636" style="9" customWidth="1"/>
+    <col min="13" max="13" width="20.9111111111111" style="8" customWidth="1"/>
+    <col min="14" max="14" width="3.45185185185185" style="9" hidden="1" customWidth="1"/>
+    <col min="15" max="16384" width="11.637037037037" style="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="48" customHeight="1" spans="1:140">
@@ -41506,11 +41506,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr codeName="Sheet3"/>
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="11.6363636363636" defaultRowHeight="15.6" outlineLevelCol="2"/>
+  <sheetFormatPr defaultColWidth="11.637037037037" defaultRowHeight="14.25" outlineLevelCol="2"/>
   <cols>
-    <col min="1" max="1" width="4.63636363636364" style="1" customWidth="1"/>
-    <col min="2" max="2" width="67.6363636363636" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="11.6363636363636" style="1" customWidth="1"/>
+    <col min="1" max="1" width="4.63703703703704" style="1" customWidth="1"/>
+    <col min="2" max="2" width="67.637037037037" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="11.637037037037" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="16.2" customHeight="1" spans="1:3">
@@ -41529,7 +41529,7 @@
       </c>
       <c r="C2" s="3"/>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" ht="15" spans="1:3">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -41574,7 +41574,7 @@
       </c>
       <c r="C7" s="3"/>
     </row>
-    <row r="8" spans="1:3">
+    <row r="8" ht="30" spans="1:3">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -41583,7 +41583,7 @@
       </c>
       <c r="C8" s="3"/>
     </row>
-    <row r="9" spans="1:3">
+    <row r="9" ht="15" spans="1:3">
       <c r="A9" s="6">
         <v>8</v>
       </c>
